--- a/Config/Datas/item_define.xlsx
+++ b/Config/Datas/item_define.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1695,6 +1695,24 @@
         <v>0</v>
       </c>
     </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>种子</t>
+        </is>
+      </c>
+      <c r="D70" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
